--- a/Documentos/MIA — Serie histórica.xlsx
+++ b/Documentos/MIA — Serie histórica.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>55.32663358118064</v>
+        <v>55.25424331606776</v>
       </c>
       <c r="C32" t="n">
-        <v>51.53705291363212</v>
+        <v>51.79219077636129</v>
       </c>
       <c r="D32" t="n">
-        <v>50.1119253295724</v>
+        <v>49.70274340039047</v>
       </c>
       <c r="E32" t="n">
-        <v>45.39014652014652</v>
+        <v>45.05467032967033</v>
       </c>
       <c r="F32" t="n">
         <v>71.68532487922705</v>
@@ -1638,12 +1638,50 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
+          <t>cerrado</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-08-05 11:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>54.26914105101671</v>
+      </c>
+      <c r="C33" t="n">
+        <v>50.80625411713648</v>
+      </c>
+      <c r="D33" t="n">
+        <v>46.67377851678921</v>
+      </c>
+      <c r="E33" t="n">
+        <v>44.94500366300366</v>
+      </c>
+      <c r="F33" t="n">
+        <v>71.50641062801931</v>
+      </c>
+      <c r="G33" t="n">
+        <v>66.51697857142858</v>
+      </c>
+      <c r="H33" t="n">
+        <v>18</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
           <t>provisional</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>2026-07-29 15:40</t>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-08-05 11:06</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:U33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3901,31 +3939,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="C32" t="n">
-        <v>77.09999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="D32" t="n">
         <v>65.8</v>
       </c>
       <c r="E32" t="n">
-        <v>85.5</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>28.2</v>
+        <v>25.2</v>
       </c>
       <c r="G32" t="n">
-        <v>66.3</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>83.90000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I32" t="n">
         <v>30</v>
       </c>
       <c r="J32" t="n">
-        <v>68.5</v>
+        <v>67.7</v>
       </c>
       <c r="K32" t="n">
         <v>100</v>
@@ -3956,12 +3994,83 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
+          <t>cerrado</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>2026-08-05 11:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C33" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="D33" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="F33" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="G33" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="H33" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="I33" t="n">
+        <v>30</v>
+      </c>
+      <c r="J33" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="K33" t="n">
+        <v>100</v>
+      </c>
+      <c r="L33" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="O33" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="P33" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>62</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>100</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
           <t>provisional</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>2026-07-29 15:40</t>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>2026-08-05 11:06</t>
         </is>
       </c>
     </row>

--- a/Documentos/MIA — Serie histórica.xlsx
+++ b/Documentos/MIA — Serie histórica.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,52 +430,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>periodo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>MIA</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>sub_Ejecutivo</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>sub_Legislativo</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>sub_Judicial</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>sub_Prensa</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>sub_Banco Central</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>cobertura_vars</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>estado</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>actualizado</t>
         </is>
@@ -1616,7 +1628,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>55.25424331606776</v>
+        <v>55.49105741381212</v>
       </c>
       <c r="C32" t="n">
         <v>51.79219077636129</v>
@@ -1631,7 +1643,7 @@
         <v>71.68532487922705</v>
       </c>
       <c r="G32" t="n">
-        <v>66.74869736842106</v>
+        <v>68.32745802005013</v>
       </c>
       <c r="H32" t="n">
         <v>18</v>
@@ -1643,7 +1655,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-05 11:06</t>
+          <t>2026-08-18 16:41</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1666,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>54.26914105101671</v>
+        <v>54.51393701137214</v>
       </c>
       <c r="C33" t="n">
         <v>50.80625411713648</v>
@@ -1669,7 +1681,7 @@
         <v>71.50641062801931</v>
       </c>
       <c r="G33" t="n">
-        <v>66.51697857142858</v>
+        <v>68.1489516404648</v>
       </c>
       <c r="H33" t="n">
         <v>18</v>
@@ -1681,7 +1693,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-05 11:06</t>
+          <t>2026-08-18 16:41</t>
         </is>
       </c>
     </row>
@@ -1700,107 +1712,107 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>periodo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>DNU vs Leyes</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Discrecionalidad presup.</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Transparencia (AIP)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ATN (federalismo)</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Eficacia de Control</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Calidad Normativa</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Costo del Legislativo</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Desempeño de la Corte</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Cobertura Judicial</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Escrutinio Abierto</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Pauta Publicitaria</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Causas contra periodistas</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Medios estatales</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Acceso de la prensa</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Financiamiento al Tesoro</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Letras intransferibles</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Designación Pdte. BCRA</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Respeto Carta Orgánica</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>estado</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>actualizado</t>
         </is>
@@ -3981,10 +3993,10 @@
         <v>65.5</v>
       </c>
       <c r="P32" t="n">
-        <v>86.90000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="Q32" t="n">
-        <v>62.8</v>
+        <v>68.8</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3999,7 +4011,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2026-08-05 11:06</t>
+          <t>2026-08-18 16:41</t>
         </is>
       </c>
     </row>
@@ -4052,10 +4064,10 @@
         <v>64.5</v>
       </c>
       <c r="P33" t="n">
-        <v>86.7</v>
+        <v>87</v>
       </c>
       <c r="Q33" t="n">
-        <v>62</v>
+        <v>68.2</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4070,7 +4082,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>2026-08-05 11:06</t>
+          <t>2026-08-18 16:41</t>
         </is>
       </c>
     </row>

--- a/Documentos/MIA — Serie histórica.xlsx
+++ b/Documentos/MIA — Serie histórica.xlsx
@@ -1666,7 +1666,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>54.51393701137214</v>
+        <v>54.5151080258649</v>
       </c>
       <c r="C33" t="n">
         <v>50.80625411713648</v>
@@ -1678,7 +1678,7 @@
         <v>44.94500366300366</v>
       </c>
       <c r="F33" t="n">
-        <v>71.50641062801931</v>
+        <v>71.51421739130434</v>
       </c>
       <c r="G33" t="n">
         <v>68.1489516404648</v>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-18 16:41</t>
+          <t>2026-08-19 10:04</t>
         </is>
       </c>
     </row>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>2026-08-18 16:41</t>
+          <t>2026-08-19 10:04</t>
         </is>
       </c>
     </row>
